--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/KANSAS_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/KANSAS_2023.xlsx
@@ -3372,7 +3372,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C168">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C273">
